--- a/artfynd/A 59401-2025 artfynd.xlsx
+++ b/artfynd/A 59401-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131695959</v>
       </c>
       <c r="B2" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131695980</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131695801</v>
       </c>
       <c r="B4" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131695971</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>131695895</v>
       </c>
       <c r="B6" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 59401-2025 artfynd.xlsx
+++ b/artfynd/A 59401-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131695959</v>
+        <v>131695801</v>
       </c>
       <c r="B2" t="n">
-        <v>79074</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -709,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bränd stubbe, Jmt</t>
+          <t>Gran, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450860</v>
+        <v>450798</v>
       </c>
       <c r="R2" t="n">
-        <v>6989647</v>
+        <v>6989917</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -776,14 +776,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131695980</v>
+        <v>131695971</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450865</v>
+        <v>450826</v>
       </c>
       <c r="R3" t="n">
-        <v>6989689</v>
+        <v>6989800</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,14 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131695801</v>
+        <v>131695980</v>
       </c>
       <c r="B4" t="n">
-        <v>79317</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -911,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gran, Jmt</t>
+          <t>Väster om Häggsåssjön , Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450798</v>
+        <v>450865</v>
       </c>
       <c r="R4" t="n">
-        <v>6989917</v>
+        <v>6989689</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131695971</v>
+        <v>131695959</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1012,14 +1012,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster om Häggsåssjön , Jmt</t>
+          <t>Bränd stubbe, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450826</v>
+        <v>450860</v>
       </c>
       <c r="R5" t="n">
-        <v>6989800</v>
+        <v>6989647</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131695895</v>
+        <v>131695998</v>
       </c>
       <c r="B6" t="n">
-        <v>58109</v>
+        <v>79130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,46 +1090,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster om Häggsåssjön , Jmt</t>
+          <t>Vid Häggsåssjön , Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450872</v>
+        <v>450959</v>
       </c>
       <c r="R6" t="n">
-        <v>6989576</v>
+        <v>6989302</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,6 +1161,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,6 +1177,333 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131695833</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väster om Häggsåssjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450826</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6989661</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131695868</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Väster om Häggsåssjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>450839</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6989626</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131695895</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Väster om Häggsåssjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>450872</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6989576</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
